--- a/public/documents/payslip.xlsx
+++ b/public/documents/payslip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeProject\highwan-tech\public\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594AD0AD-9CAF-4095-9F79-48ADEDE913A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A07C45D-2C88-4CE4-9C66-D88CB573B9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,30 +826,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -862,52 +884,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1200,32 +1200,32 @@
     <row r="1" spans="1:8" ht="27" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="5"/>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
       <c r="A3" s="5"/>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
@@ -1274,34 +1274,34 @@
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1">
       <c r="A9" s="5"/>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="47"/>
-      <c r="E9" s="48" t="s">
+      <c r="D9" s="76"/>
+      <c r="E9" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="77"/>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1">
       <c r="A10" s="5"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="49" t="s">
+      <c r="B10" s="48"/>
+      <c r="C10" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="50"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="11">
         <v>26</v>
       </c>
@@ -1312,11 +1312,11 @@
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1">
       <c r="A11" s="5"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="51" t="s">
+      <c r="B11" s="48"/>
+      <c r="C11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="60"/>
       <c r="E11" s="13">
         <v>0</v>
       </c>
@@ -1327,11 +1327,11 @@
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="51" t="s">
+      <c r="B12" s="48"/>
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="52"/>
+      <c r="D12" s="60"/>
       <c r="E12" s="15">
         <v>1</v>
       </c>
@@ -1342,11 +1342,11 @@
     </row>
     <row r="13" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="51" t="s">
+      <c r="B13" s="48"/>
+      <c r="C13" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="52"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="13">
         <v>0</v>
       </c>
@@ -1358,11 +1358,11 @@
     </row>
     <row r="14" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="5"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="51" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="52"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="15">
         <v>2</v>
       </c>
@@ -1374,11 +1374,11 @@
     </row>
     <row r="15" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A15" s="5"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="53" t="s">
+      <c r="B15" s="48"/>
+      <c r="C15" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="54"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="16">
         <v>24</v>
       </c>
@@ -1390,11 +1390,11 @@
     </row>
     <row r="16" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A16" s="5"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="51" t="s">
+      <c r="B16" s="48"/>
+      <c r="C16" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="52"/>
+      <c r="D16" s="60"/>
       <c r="E16" s="13">
         <v>32</v>
       </c>
@@ -1406,11 +1406,11 @@
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1">
       <c r="A17" s="5"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="51" t="s">
+      <c r="B17" s="48"/>
+      <c r="C17" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="52"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="13">
         <v>0</v>
       </c>
@@ -1421,11 +1421,11 @@
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1">
       <c r="A18" s="5"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="51" t="s">
+      <c r="B18" s="48"/>
+      <c r="C18" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="52"/>
+      <c r="D18" s="60"/>
       <c r="E18" s="13">
         <v>0</v>
       </c>
@@ -1436,11 +1436,11 @@
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1">
       <c r="A19" s="5"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="51" t="s">
+      <c r="B19" s="48"/>
+      <c r="C19" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="52"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="13">
         <v>0</v>
       </c>
@@ -1451,11 +1451,11 @@
     </row>
     <row r="20" spans="1:7" ht="18" customHeight="1">
       <c r="A20" s="5"/>
-      <c r="B20" s="67"/>
-      <c r="C20" s="51" t="s">
+      <c r="B20" s="48"/>
+      <c r="C20" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="52"/>
+      <c r="D20" s="60"/>
       <c r="E20" s="13">
         <v>0</v>
       </c>
@@ -1466,11 +1466,11 @@
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1">
       <c r="A21" s="5"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="51" t="s">
+      <c r="B21" s="48"/>
+      <c r="C21" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="52"/>
+      <c r="D21" s="60"/>
       <c r="E21" s="13">
         <v>0</v>
       </c>
@@ -1481,11 +1481,11 @@
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1">
       <c r="A22" s="5"/>
-      <c r="B22" s="67"/>
-      <c r="C22" s="51" t="s">
+      <c r="B22" s="48"/>
+      <c r="C22" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="60"/>
       <c r="E22" s="13">
         <v>5000000</v>
       </c>
@@ -1496,11 +1496,11 @@
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1">
       <c r="A23" s="5"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="51" t="s">
+      <c r="B23" s="48"/>
+      <c r="C23" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="52"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="18">
         <v>1500000</v>
       </c>
@@ -1511,11 +1511,11 @@
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1">
       <c r="A24" s="5"/>
-      <c r="B24" s="67"/>
-      <c r="C24" s="55" t="s">
+      <c r="B24" s="48"/>
+      <c r="C24" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="56"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="19">
         <v>6000000</v>
       </c>
@@ -1526,24 +1526,24 @@
     </row>
     <row r="25" spans="1:7" ht="18" customHeight="1">
       <c r="A25" s="5"/>
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="60"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" ht="18" customHeight="1">
       <c r="A26" s="5"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="51" t="s">
+      <c r="B26" s="50"/>
+      <c r="C26" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="52"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="13">
         <v>461538</v>
       </c>
@@ -1554,11 +1554,11 @@
     </row>
     <row r="27" spans="1:7" ht="18" customHeight="1">
       <c r="A27" s="5"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="61" t="s">
+      <c r="B27" s="50"/>
+      <c r="C27" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="62"/>
+      <c r="D27" s="53"/>
       <c r="E27" s="13"/>
       <c r="F27" s="21" t="s">
         <v>27</v>
@@ -1567,11 +1567,11 @@
     </row>
     <row r="28" spans="1:7" ht="18" customHeight="1">
       <c r="A28" s="5"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="61" t="s">
+      <c r="B28" s="50"/>
+      <c r="C28" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="62"/>
+      <c r="D28" s="53"/>
       <c r="E28" s="13"/>
       <c r="F28" s="21" t="s">
         <v>27</v>
@@ -1580,11 +1580,11 @@
     </row>
     <row r="29" spans="1:7" ht="18" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="61" t="s">
+      <c r="B29" s="50"/>
+      <c r="C29" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="62"/>
+      <c r="D29" s="53"/>
       <c r="E29" s="13"/>
       <c r="F29" s="21" t="s">
         <v>27</v>
@@ -1593,11 +1593,11 @@
     </row>
     <row r="30" spans="1:7" ht="18" customHeight="1">
       <c r="A30" s="5"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="51" t="s">
+      <c r="B30" s="50"/>
+      <c r="C30" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="60"/>
       <c r="E30" s="13">
         <v>1153846</v>
       </c>
@@ -1608,11 +1608,11 @@
     </row>
     <row r="31" spans="1:7" ht="18" customHeight="1">
       <c r="A31" s="5"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="51" t="s">
+      <c r="B31" s="50"/>
+      <c r="C31" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="52"/>
+      <c r="D31" s="60"/>
       <c r="E31" s="13">
         <v>240000</v>
       </c>
@@ -1623,11 +1623,11 @@
     </row>
     <row r="32" spans="1:7" ht="18" customHeight="1">
       <c r="A32" s="5"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="51" t="s">
+      <c r="B32" s="50"/>
+      <c r="C32" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="52"/>
+      <c r="D32" s="60"/>
       <c r="E32" s="22"/>
       <c r="F32" s="21" t="s">
         <v>27</v>
@@ -1636,11 +1636,11 @@
     </row>
     <row r="33" spans="1:7" ht="18" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="51" t="s">
+      <c r="B33" s="50"/>
+      <c r="C33" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="52"/>
+      <c r="D33" s="60"/>
       <c r="E33" s="22"/>
       <c r="F33" s="21" t="s">
         <v>27</v>
@@ -1649,11 +1649,11 @@
     </row>
     <row r="34" spans="1:7" ht="18" customHeight="1">
       <c r="A34" s="5"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="51" t="s">
+      <c r="B34" s="50"/>
+      <c r="C34" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="52"/>
+      <c r="D34" s="60"/>
       <c r="E34" s="22"/>
       <c r="F34" s="21" t="s">
         <v>27</v>
@@ -1662,11 +1662,11 @@
     </row>
     <row r="35" spans="1:7" ht="18" customHeight="1">
       <c r="A35" s="5"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="61" t="s">
+      <c r="B35" s="50"/>
+      <c r="C35" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="62"/>
+      <c r="D35" s="53"/>
       <c r="E35" s="23"/>
       <c r="F35" s="21" t="s">
         <v>27</v>
@@ -1675,11 +1675,11 @@
     </row>
     <row r="36" spans="1:7" ht="18" customHeight="1">
       <c r="A36" s="5"/>
-      <c r="B36" s="69"/>
-      <c r="C36" s="51" t="s">
+      <c r="B36" s="50"/>
+      <c r="C36" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="57"/>
+      <c r="D36" s="63"/>
       <c r="E36" s="23"/>
       <c r="F36" s="21" t="s">
         <v>27</v>
@@ -1688,12 +1688,14 @@
     </row>
     <row r="37" spans="1:7" ht="18" customHeight="1">
       <c r="A37" s="5"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="76" t="s">
+      <c r="B37" s="50"/>
+      <c r="C37" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="77"/>
-      <c r="E37" s="23"/>
+      <c r="D37" s="68"/>
+      <c r="E37" s="23">
+        <v>240000</v>
+      </c>
       <c r="F37" s="21" t="s">
         <v>27</v>
       </c>
@@ -1701,11 +1703,11 @@
     </row>
     <row r="38" spans="1:7" ht="18" customHeight="1">
       <c r="A38" s="5"/>
-      <c r="B38" s="69"/>
-      <c r="C38" s="55" t="s">
+      <c r="B38" s="50"/>
+      <c r="C38" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="56"/>
+      <c r="D38" s="62"/>
       <c r="E38" s="24">
         <v>2545385</v>
       </c>
@@ -1716,22 +1718,22 @@
     </row>
     <row r="39" spans="1:7" ht="18" customHeight="1">
       <c r="A39" s="5"/>
-      <c r="B39" s="69"/>
-      <c r="C39" s="71" t="s">
+      <c r="B39" s="50"/>
+      <c r="C39" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="73"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="56"/>
       <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" ht="18" customHeight="1">
       <c r="A40" s="5"/>
-      <c r="B40" s="69"/>
-      <c r="C40" s="74" t="s">
+      <c r="B40" s="50"/>
+      <c r="C40" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="75"/>
+      <c r="D40" s="58"/>
       <c r="E40" s="25">
         <v>525000</v>
       </c>
@@ -1742,11 +1744,11 @@
     </row>
     <row r="41" spans="1:7" ht="18" customHeight="1">
       <c r="A41" s="5"/>
-      <c r="B41" s="69"/>
-      <c r="C41" s="51" t="s">
+      <c r="B41" s="50"/>
+      <c r="C41" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="52"/>
+      <c r="D41" s="60"/>
       <c r="E41" s="27" t="s">
         <v>41</v>
       </c>
@@ -1757,11 +1759,11 @@
     </row>
     <row r="42" spans="1:7" ht="18" customHeight="1">
       <c r="A42" s="5"/>
-      <c r="B42" s="69"/>
-      <c r="C42" s="51" t="s">
+      <c r="B42" s="50"/>
+      <c r="C42" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="52"/>
+      <c r="D42" s="60"/>
       <c r="E42" s="27" t="s">
         <v>41</v>
       </c>
@@ -1772,11 +1774,11 @@
     </row>
     <row r="43" spans="1:7" ht="18" customHeight="1">
       <c r="A43" s="5"/>
-      <c r="B43" s="69"/>
-      <c r="C43" s="55" t="s">
+      <c r="B43" s="50"/>
+      <c r="C43" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="56"/>
+      <c r="D43" s="62"/>
       <c r="E43" s="29">
         <v>525000</v>
       </c>
@@ -1787,11 +1789,11 @@
     </row>
     <row r="44" spans="1:7" ht="18" customHeight="1">
       <c r="A44" s="5"/>
-      <c r="B44" s="70"/>
-      <c r="C44" s="63" t="s">
+      <c r="B44" s="51"/>
+      <c r="C44" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="64"/>
+      <c r="D44" s="44"/>
       <c r="E44" s="31">
         <f>E24+E38-E43</f>
         <v>8020385</v>
@@ -1813,19 +1815,19 @@
     <row r="46" spans="1:7" ht="18" customHeight="1">
       <c r="A46" s="5"/>
       <c r="C46" s="6"/>
-      <c r="D46" s="44" t="s">
+      <c r="D46" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="44"/>
+      <c r="E46" s="45"/>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:7" ht="18" customHeight="1">
       <c r="A47" s="5"/>
       <c r="C47" s="37"/>
-      <c r="D47" s="65" t="s">
+      <c r="D47" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="65"/>
+      <c r="E47" s="46"/>
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:7" ht="18" customHeight="1">
@@ -1844,10 +1846,10 @@
     <row r="50" spans="1:7" ht="18" customHeight="1">
       <c r="A50" s="5"/>
       <c r="C50" s="6"/>
-      <c r="D50" s="44" t="s">
+      <c r="D50" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E50" s="44"/>
+      <c r="E50" s="45"/>
       <c r="G50" s="7"/>
     </row>
     <row r="51" spans="1:7" ht="18" customHeight="1">
@@ -1861,6 +1863,36 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="D47:E47"/>
@@ -1877,36 +1909,6 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" scale="70" orientation="portrait"/>
